--- a/dtm_dashboard/excel_data/keeping_prr/Баумана/Апрель 2026.xlsx
+++ b/dtm_dashboard/excel_data/keeping_prr/Баумана/Апрель 2026.xlsx
@@ -23,9 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>Остатки и обороты в тоннах по дням с 01.04.2026 по 14.04.2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Остатки и обороты в тоннах по дням с 01.04.2026 по 19.04.2026</t>
   </si>
   <si>
     <t>Отбор:</t>
@@ -92,6 +92,21 @@
   </si>
   <si>
     <t>14.04.2026</t>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+  </si>
+  <si>
+    <t>16.04.2026</t>
+  </si>
+  <si>
+    <t>17.04.2026</t>
+  </si>
+  <si>
+    <t>18.04.2026</t>
+  </si>
+  <si>
+    <t>19.04.2026</t>
   </si>
   <si>
     <t>Итого</t>
@@ -159,7 +174,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -223,37 +238,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="A0A0A0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="A0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="A0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="A0A0A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="A0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="A0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -303,13 +292,7 @@
     <xf numFmtId="51" fontId="3" fillId="2" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="top" wrapText="0"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="5" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="top" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="2" borderId="6" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="top" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="2" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="53" fontId="3" fillId="2" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -331,7 +314,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false" fitToPage="false"/>
   </sheetPr>
-  <dimension ref="J21"/>
+  <dimension ref="J26"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="8.66796875" style="1" customWidth="true"/>
@@ -665,37 +648,143 @@
       <c r="D20" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="E20" s="11" t="n">
-        <v>132</v>
-      </c>
-      <c r="F20" s="11" t="e"/>
+      <c r="E20" s="12" t="n">
+        <v>349.6</v>
+      </c>
+      <c r="F20" s="12" t="e"/>
       <c r="G20" s="7" t="n">
-        <v>7738.014</v>
-      </c>
-      <c r="H20" s="8" t="e"/>
-      <c r="I20" s="9" t="e"/>
-      <c r="J20" s="10" t="e"/>
-    </row>
-    <row r="21" ht="13" customHeight="true">
-      <c r="A21" s="15" t="s">
+        <v>7520.414</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="I20" s="13" t="e"/>
+      <c r="J20" s="13" t="n">
+        <v>1.375</v>
+      </c>
+    </row>
+    <row r="21" ht="11" customHeight="true">
+      <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="15" t="e"/>
-      <c r="C21" s="15" t="e"/>
-      <c r="D21" s="16" t="n">
-        <v>2512.524</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>2710.625</v>
-      </c>
-      <c r="F21" s="16" t="e"/>
-      <c r="G21" s="15" t="e"/>
-      <c r="H21" s="17" t="e"/>
-      <c r="I21" s="18" t="e"/>
-      <c r="J21" s="19" t="e"/>
+      <c r="B21" s="5" t="e"/>
+      <c r="C21" s="5" t="e"/>
+      <c r="D21" s="13" t="n">
+        <v>16.389</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>176.875</v>
+      </c>
+      <c r="F21" s="13" t="e"/>
+      <c r="G21" s="7" t="n">
+        <v>7359.928</v>
+      </c>
+      <c r="H21" s="8" t="e"/>
+      <c r="I21" s="9" t="e"/>
+      <c r="J21" s="10" t="e"/>
+    </row>
+    <row r="22" ht="11" customHeight="true">
+      <c r="A22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="5" t="e"/>
+      <c r="C22" s="5" t="e"/>
+      <c r="D22" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>220</v>
+      </c>
+      <c r="F22" s="11" t="e"/>
+      <c r="G22" s="7" t="n">
+        <v>7184.928</v>
+      </c>
+      <c r="H22" s="8" t="e"/>
+      <c r="I22" s="9" t="e"/>
+      <c r="J22" s="10" t="e"/>
+    </row>
+    <row r="23" ht="11" customHeight="true">
+      <c r="A23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="5" t="e"/>
+      <c r="C23" s="5" t="e"/>
+      <c r="D23" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>189.875</v>
+      </c>
+      <c r="F23" s="13" t="e"/>
+      <c r="G23" s="7" t="n">
+        <v>7084.053</v>
+      </c>
+      <c r="H23" s="8" t="e"/>
+      <c r="I23" s="9" t="e"/>
+      <c r="J23" s="10" t="e"/>
+    </row>
+    <row r="24" ht="11" customHeight="true">
+      <c r="A24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="5" t="e"/>
+      <c r="C24" s="5" t="e"/>
+      <c r="D24" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>224</v>
+      </c>
+      <c r="F24" s="11" t="e"/>
+      <c r="G24" s="7" t="n">
+        <v>6882.553</v>
+      </c>
+      <c r="H24" s="8" t="e"/>
+      <c r="I24" s="9" t="e"/>
+      <c r="J24" s="10" t="e"/>
+    </row>
+    <row r="25" ht="11" customHeight="true">
+      <c r="A25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="5" t="e"/>
+      <c r="C25" s="5" t="e"/>
+      <c r="D25" s="10" t="e"/>
+      <c r="E25" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="F25" s="11" t="e"/>
+      <c r="G25" s="7" t="n">
+        <v>6838.553</v>
+      </c>
+      <c r="H25" s="8" t="e"/>
+      <c r="I25" s="9" t="e"/>
+      <c r="J25" s="10" t="e"/>
+    </row>
+    <row r="26" ht="13" customHeight="true">
+      <c r="A26" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="15" t="e"/>
+      <c r="C26" s="15" t="e"/>
+      <c r="D26" s="16" t="n">
+        <v>2685.413</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>3782.975</v>
+      </c>
+      <c r="F26" s="16" t="e"/>
+      <c r="G26" s="15" t="e"/>
+      <c r="H26" s="17" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="I26" s="17" t="e"/>
+      <c r="J26" s="17" t="n">
+        <v>1.375</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="45">
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="H6:I6"/>
@@ -727,8 +816,20 @@
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="H20:I20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="H26:I26"/>
   </mergeCells>
   <pageMargins left="0.393700787401574803149606299" top="0.393700787401574803149606299" right="0.393700787401574803149606299" bottom="0.393700787401574803149606299" header="0" footer="0"/>
   <pageSetup blackAndWhite="false" scale="100" pageOrder="overThenDown" orientation="portrait"/>

--- a/dtm_dashboard/excel_data/keeping_prr/Баумана/Апрель 2026.xlsx
+++ b/dtm_dashboard/excel_data/keeping_prr/Баумана/Апрель 2026.xlsx
@@ -23,9 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>Остатки и обороты в тоннах по дням с 01.04.2026 по 19.04.2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+  <si>
+    <t>Остатки и обороты в тоннах по дням с 01.04.2026 по 30.04.2026</t>
   </si>
   <si>
     <t>Отбор:</t>
@@ -107,6 +107,39 @@
   </si>
   <si>
     <t>19.04.2026</t>
+  </si>
+  <si>
+    <t>20.04.2026</t>
+  </si>
+  <si>
+    <t>21.04.2026</t>
+  </si>
+  <si>
+    <t>22.04.2026</t>
+  </si>
+  <si>
+    <t>23.04.2026</t>
+  </si>
+  <si>
+    <t>24.04.2026</t>
+  </si>
+  <si>
+    <t>25.04.2026</t>
+  </si>
+  <si>
+    <t>26.04.2026</t>
+  </si>
+  <si>
+    <t>27.04.2026</t>
+  </si>
+  <si>
+    <t>28.04.2026</t>
+  </si>
+  <si>
+    <t>29.04.2026</t>
+  </si>
+  <si>
+    <t>30.04.2026</t>
   </si>
   <si>
     <t>Итого</t>
@@ -314,7 +347,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false" fitToPage="false"/>
   </sheetPr>
-  <dimension ref="J26"/>
+  <dimension ref="J37"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="8.66796875" style="1" customWidth="true"/>
@@ -761,30 +794,246 @@
       <c r="I25" s="9" t="e"/>
       <c r="J25" s="10" t="e"/>
     </row>
-    <row r="26" ht="13" customHeight="true">
-      <c r="A26" s="15" t="s">
+    <row r="26" ht="11" customHeight="true">
+      <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="15" t="e"/>
-      <c r="C26" s="15" t="e"/>
-      <c r="D26" s="16" t="n">
-        <v>2685.413</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>3782.975</v>
-      </c>
-      <c r="F26" s="16" t="e"/>
-      <c r="G26" s="15" t="e"/>
-      <c r="H26" s="17" t="n">
+      <c r="B26" s="5" t="e"/>
+      <c r="C26" s="5" t="e"/>
+      <c r="D26" s="10" t="e"/>
+      <c r="E26" s="11" t="n">
+        <v>132</v>
+      </c>
+      <c r="F26" s="11" t="e"/>
+      <c r="G26" s="7" t="n">
+        <v>6706.553</v>
+      </c>
+      <c r="H26" s="8" t="e"/>
+      <c r="I26" s="9" t="e"/>
+      <c r="J26" s="10" t="e"/>
+    </row>
+    <row r="27" ht="11" customHeight="true">
+      <c r="A27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="5" t="e"/>
+      <c r="C27" s="5" t="e"/>
+      <c r="D27" s="10" t="e"/>
+      <c r="E27" s="6" t="n">
+        <v>232.05</v>
+      </c>
+      <c r="F27" s="6" t="e"/>
+      <c r="G27" s="7" t="n">
+        <v>6474.503</v>
+      </c>
+      <c r="H27" s="8" t="e"/>
+      <c r="I27" s="9" t="e"/>
+      <c r="J27" s="10" t="e"/>
+    </row>
+    <row r="28" ht="11" customHeight="true">
+      <c r="A28" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="5" t="e"/>
+      <c r="C28" s="5" t="e"/>
+      <c r="D28" s="12" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="F28" s="6" t="e"/>
+      <c r="G28" s="7" t="n">
+        <v>6487.253</v>
+      </c>
+      <c r="H28" s="8" t="e"/>
+      <c r="I28" s="9" t="e"/>
+      <c r="J28" s="10" t="e"/>
+    </row>
+    <row r="29" ht="11" customHeight="true">
+      <c r="A29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="5" t="e"/>
+      <c r="C29" s="5" t="e"/>
+      <c r="D29" s="13" t="n">
+        <v>406.475</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="F29" s="12" t="e"/>
+      <c r="G29" s="7" t="n">
+        <v>6646.228</v>
+      </c>
+      <c r="H29" s="8" t="e"/>
+      <c r="I29" s="9" t="e"/>
+      <c r="J29" s="10" t="e"/>
+    </row>
+    <row r="30" ht="11" customHeight="true">
+      <c r="A30" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="5" t="e"/>
+      <c r="C30" s="5" t="e"/>
+      <c r="D30" s="11" t="n">
+        <v>201</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F30" s="12" t="e"/>
+      <c r="G30" s="7" t="n">
+        <v>6825.128</v>
+      </c>
+      <c r="H30" s="8" t="e"/>
+      <c r="I30" s="9" t="e"/>
+      <c r="J30" s="10" t="e"/>
+    </row>
+    <row r="31" ht="11" customHeight="true">
+      <c r="A31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="5" t="e"/>
+      <c r="C31" s="5" t="e"/>
+      <c r="D31" s="13" t="n">
+        <v>207.147</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="F31" s="11" t="e"/>
+      <c r="G31" s="7" t="n">
+        <v>7010.275</v>
+      </c>
+      <c r="H31" s="8" t="e"/>
+      <c r="I31" s="9" t="e"/>
+      <c r="J31" s="10" t="e"/>
+    </row>
+    <row r="32" ht="11" customHeight="true">
+      <c r="A32" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="5" t="e"/>
+      <c r="C32" s="5" t="e"/>
+      <c r="D32" s="12" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="F32" s="11" t="e"/>
+      <c r="G32" s="7" t="n">
+        <v>7143.775</v>
+      </c>
+      <c r="H32" s="8" t="e"/>
+      <c r="I32" s="9" t="e"/>
+      <c r="J32" s="10" t="e"/>
+    </row>
+    <row r="33" ht="11" customHeight="true">
+      <c r="A33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="5" t="e"/>
+      <c r="C33" s="5" t="e"/>
+      <c r="D33" s="12" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>150.489</v>
+      </c>
+      <c r="F33" s="13" t="e"/>
+      <c r="G33" s="7" t="n">
+        <v>7059.786</v>
+      </c>
+      <c r="H33" s="8" t="e"/>
+      <c r="I33" s="9" t="e"/>
+      <c r="J33" s="10" t="e"/>
+    </row>
+    <row r="34" ht="11" customHeight="true">
+      <c r="A34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="5" t="e"/>
+      <c r="C34" s="5" t="e"/>
+      <c r="D34" s="11" t="n">
+        <v>157</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>65.875</v>
+      </c>
+      <c r="F34" s="13" t="e"/>
+      <c r="G34" s="7" t="n">
+        <v>7150.911</v>
+      </c>
+      <c r="H34" s="8" t="e"/>
+      <c r="I34" s="9" t="e"/>
+      <c r="J34" s="10" t="e"/>
+    </row>
+    <row r="35" ht="11" customHeight="true">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="e"/>
+      <c r="C35" s="5" t="e"/>
+      <c r="D35" s="11" t="n">
+        <v>156</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>316.76</v>
+      </c>
+      <c r="F35" s="6" t="e"/>
+      <c r="G35" s="7" t="n">
+        <v>6990.151</v>
+      </c>
+      <c r="H35" s="8" t="e"/>
+      <c r="I35" s="9" t="e"/>
+      <c r="J35" s="10" t="e"/>
+    </row>
+    <row r="36" ht="11" customHeight="true">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="e"/>
+      <c r="C36" s="5" t="e"/>
+      <c r="D36" s="11" t="n">
+        <v>111</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>171.625</v>
+      </c>
+      <c r="F36" s="13" t="e"/>
+      <c r="G36" s="7" t="n">
+        <v>6929.526</v>
+      </c>
+      <c r="H36" s="8" t="e"/>
+      <c r="I36" s="9" t="e"/>
+      <c r="J36" s="10" t="e"/>
+    </row>
+    <row r="37" ht="13" customHeight="true">
+      <c r="A37" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="15" t="e"/>
+      <c r="C37" s="15" t="e"/>
+      <c r="D37" s="16" t="n">
+        <v>4324.535</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>5331.124</v>
+      </c>
+      <c r="F37" s="16" t="e"/>
+      <c r="G37" s="15" t="e"/>
+      <c r="H37" s="17" t="n">
         <v>1.375</v>
       </c>
-      <c r="I26" s="17" t="e"/>
-      <c r="J26" s="17" t="n">
+      <c r="I37" s="17" t="e"/>
+      <c r="J37" s="17" t="n">
         <v>1.375</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="67">
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="H6:I6"/>
@@ -829,7 +1078,29 @@
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="E26:F26"/>
-    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="H37:I37"/>
   </mergeCells>
   <pageMargins left="0.393700787401574803149606299" top="0.393700787401574803149606299" right="0.393700787401574803149606299" bottom="0.393700787401574803149606299" header="0" footer="0"/>
   <pageSetup blackAndWhite="false" scale="100" pageOrder="overThenDown" orientation="portrait"/>
